--- a/outputs/llm/gemini/classification_pi_total/channel_results_051.xlsx
+++ b/outputs/llm/gemini/classification_pi_total/channel_results_051.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,48 +471,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>:newstime</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>5.203703703703703</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.6296296296296297</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5.203703703703703</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.6296296296296297</v>
-      </c>
+          <t>3nach9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AFP Deutsch</t>
+          <t>:newstime</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.907407407407407</v>
+        <v>5.203703703703703</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5370370370370371</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
@@ -521,217 +509,217 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4.907407407407407</v>
+        <v>5.203703703703703</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5370370370370371</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="H3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARTEde</t>
+          <t>AFP Deutsch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.428571428571428</v>
+        <v>4.907407407407407</v>
       </c>
       <c r="C4" t="n">
-        <v>3.214285714285714</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3.428571428571428</v>
+        <v>4.907407407407407</v>
       </c>
       <c r="G4" t="n">
-        <v>3.214285714285714</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I4" t="n">
-        <v>0.125</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="J4" t="n">
-        <v>0.125</v>
+        <v>0.1290322580645161</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Achgut</t>
+          <t>ARTEde</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.5</v>
+        <v>3.428571428571428</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="D5" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="F5" t="n">
-        <v>8.5</v>
+        <v>3.428571428571428</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AfD TV</t>
+          <t>Achgut</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.5625</v>
+        <v>8.5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.46875</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="E6" t="n">
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>8.585106382978724</v>
+        <v>8.5</v>
       </c>
       <c r="G6" t="n">
-        <v>8.51063829787234</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AfD-Fraktion Bundestag</t>
+          <t>AfD TV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.866666666666666</v>
+        <v>8.5625</v>
       </c>
       <c r="C7" t="n">
-        <v>7.8</v>
+        <v>8.46875</v>
       </c>
       <c r="D7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>7.866666666666666</v>
+        <v>8.585106382978724</v>
       </c>
       <c r="G7" t="n">
-        <v>7.8</v>
+        <v>8.51063829787234</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AfD-Fraktion NRW</t>
+          <t>AfD im EU-Parlament</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.544642857142857</v>
+        <v>7.4375</v>
       </c>
       <c r="C8" t="n">
-        <v>7.473214285714286</v>
+        <v>7.234375</v>
       </c>
       <c r="D8" t="n">
         <v>7.5</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="F8" t="n">
-        <v>7.545454545454546</v>
+        <v>7.416666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>7.454545454545454</v>
+        <v>7.15</v>
       </c>
       <c r="H8" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.05882352941176471</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aktien mit Kopf</t>
+          <t>AfD-Fraktion Bundestag</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.36</v>
+        <v>7.866666666666666</v>
       </c>
       <c r="C9" t="n">
-        <v>7.861666666666666</v>
+        <v>7.8</v>
       </c>
       <c r="D9" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="E9" t="n">
         <v>8.5</v>
       </c>
       <c r="F9" t="n">
-        <v>7.172727272727273</v>
+        <v>7.866666666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>7.259090909090909</v>
+        <v>7.8</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -743,29 +731,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alice Weidel</t>
+          <t>AfD-Fraktion NRW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.928571428571429</v>
+        <v>7.544642857142857</v>
       </c>
       <c r="C10" t="n">
-        <v>8.5</v>
+        <v>7.473214285714286</v>
       </c>
       <c r="D10" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>7.928571428571429</v>
+        <v>7.545454545454546</v>
       </c>
       <c r="G10" t="n">
-        <v>8.5</v>
+        <v>7.454545454545454</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -777,240 +765,244 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aljosha</t>
+          <t>Aktien mit Kopf</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.166666666666667</v>
+        <v>7.332432432432433</v>
       </c>
       <c r="C11" t="n">
-        <v>2.476190476190476</v>
+        <v>7.752702702702703</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>7.225000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>4.5</v>
+        <v>7.167857142857143</v>
       </c>
       <c r="H11" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08695652173913043</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08695652173913043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Andreas Schmitz (Der Akku Doktor)</t>
+          <t>Alice Weidel</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>7.928571428571429</v>
       </c>
       <c r="C12" t="n">
-        <v>3.055555555555555</v>
+        <v>8.5</v>
       </c>
       <c r="D12" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>7.928571428571429</v>
       </c>
       <c r="G12" t="n">
-        <v>3.055555555555555</v>
+        <v>8.5</v>
       </c>
       <c r="H12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Auch Staiy</t>
+          <t>Aljosha</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.40625</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="C13" t="n">
-        <v>4.1875</v>
+        <v>2.476190476190476</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>4.125</v>
+        <v>2.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="H13" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BILD</t>
+          <t>Andreas Schmitz (Der Akku Doktor)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.181818181818182</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3695652173913043</v>
+        <v>3.055555555555555</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="F14" t="n">
-        <v>5.181818181818182</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3863636363636364</v>
+        <v>3.055555555555555</v>
       </c>
       <c r="H14" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BR24</t>
+          <t>Auch Staiy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.9375</v>
+        <v>3.40625</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5</v>
+        <v>4.1875</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="F15" t="n">
-        <v>4.9375</v>
+        <v>4.125</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04</v>
+        <v>0.5428571428571428</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Best of Bud Spencer &amp; Terence Hill</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>BILD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5.181818181818182</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.3695652173913043</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.181818181818182</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3863636363636364</v>
+      </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0.3947368421052632</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Boris von Morgenstern</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>7.444444444444445</v>
-      </c>
+          <t>BOSS  DELUXE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>8.111111111111111</v>
-      </c>
-      <c r="D17" t="n">
-        <v>8</v>
-      </c>
+        <v>7.166666666666667</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>8.125</v>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Breaking Lab</t>
+          <t>BR24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.633333333333334</v>
+        <v>4.9375</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -1019,115 +1011,103 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>4.633333333333334</v>
+        <v>4.9375</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.04</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>COMPACT-TV</t>
+          <t>Berlin360°</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.19047619047619</v>
+        <v>1.5</v>
       </c>
       <c r="C19" t="n">
-        <v>8.547619047619047</v>
+        <v>6.5</v>
       </c>
       <c r="D19" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="F19" t="n">
-        <v>7.933333333333334</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="n">
-        <v>8.233333333333333</v>
+        <v>6.5</v>
       </c>
       <c r="H19" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.9827586206896551</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.9827586206896551</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Carsten Jahn - TEAM HEIMAT</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>7.405</v>
-      </c>
-      <c r="C20" t="n">
-        <v>8.613333333333333</v>
-      </c>
-      <c r="D20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E20" t="n">
-        <v>9</v>
-      </c>
-      <c r="F20" t="n">
-        <v>7.413043478260869</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8.391304347826088</v>
-      </c>
+          <t>Best of Bud Spencer &amp; Terence Hill</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Clownswelt</t>
+          <t>Boris Reitschuster</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.985714285714286</v>
+        <v>7.735294117647059</v>
       </c>
       <c r="C21" t="n">
-        <v>8.728571428571428</v>
+        <v>8.720588235294118</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E21" t="n">
         <v>8.5</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="G21" t="n">
-        <v>8.875</v>
+        <v>8.766666666666667</v>
       </c>
       <c r="H21" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1139,48 +1119,48 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DER AKTIONÄR TV</t>
+          <t>Boris von Morgenstern</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>7.444444444444445</v>
       </c>
       <c r="C22" t="n">
-        <v>1.625</v>
+        <v>8.111111111111111</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="G22" t="n">
-        <v>1.625</v>
+        <v>8.125</v>
       </c>
       <c r="H22" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="I22" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DER SPIEGEL</t>
+          <t>Breaking Lab</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.096153846153846</v>
+        <v>4.633333333333334</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="D23" t="n">
         <v>5</v>
@@ -1189,81 +1169,81 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>5.096153846153846</v>
+        <v>4.633333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DER STANDARD</t>
+          <t>COMPACT-TV</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.238095238095238</v>
+        <v>8.19047619047619</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2142857142857143</v>
+        <v>8.547619047619047</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F24" t="n">
-        <v>4.238095238095238</v>
+        <v>7.933333333333334</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2142857142857143</v>
+        <v>8.233333333333333</v>
       </c>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.04545454545454546</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.04545454545454546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DIE DA OBEN!</t>
+          <t>Carsten Jahn - TEAM HEIMAT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.75</v>
+        <v>7.405</v>
       </c>
       <c r="C25" t="n">
-        <v>1.85</v>
+        <v>8.613333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>3.611111111111111</v>
+        <v>7.413043478260869</v>
       </c>
       <c r="G25" t="n">
-        <v>2.055555555555555</v>
+        <v>8.391304347826088</v>
       </c>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1275,236 +1255,236 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DIE WELTWOCHE</t>
+          <t>Cashkurs.com</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.771666666666667</v>
+        <v>7.625</v>
       </c>
       <c r="C26" t="n">
-        <v>7.461666666666667</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="D26" t="n">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="E26" t="n">
         <v>8.5</v>
       </c>
       <c r="F26" t="n">
-        <v>7.70925925925926</v>
+        <v>7.625</v>
       </c>
       <c r="G26" t="n">
-        <v>7.327777777777778</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIE ZEIT </t>
+          <t>Claus Roppel</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.967741935483871</v>
+        <v>7.133333333333334</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4516129032258064</v>
+        <v>5.67741935483871</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="F27" t="n">
-        <v>4.966666666666667</v>
+        <v>7.120689655172414</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4666666666666667</v>
+        <v>5.65</v>
       </c>
       <c r="H27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I27" t="n">
-        <v>0.03125</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="J27" t="n">
-        <v>0.03125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DW Deutsch</t>
+          <t>Clownswelt</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.195652173913044</v>
+        <v>7.985714285714286</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6956521739130435</v>
+        <v>8.728571428571428</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="F28" t="n">
-        <v>4.195652173913044</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6956521739130435</v>
+        <v>8.875</v>
       </c>
       <c r="H28" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dekarldent</t>
+          <t>DER AKTIONÄR TV</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.007317073170732</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>5.804878048780488</v>
+        <v>1.625</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>7.1875</v>
+        <v>1.625</v>
       </c>
       <c r="H29" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I29" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.95</v>
       </c>
       <c r="J29" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Der Dunkle Parabelritter</t>
+          <t>DER SPIEGEL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.888888888888889</v>
+        <v>5.096153846153846</v>
       </c>
       <c r="C30" t="n">
-        <v>2.222222222222222</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>3.2</v>
+        <v>5.096153846153846</v>
       </c>
       <c r="G30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.2121212121212121</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Der Medienfuzzi</t>
+          <t>DER STANDARD</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7.352272727272728</v>
+        <v>4.238095238095238</v>
       </c>
       <c r="C31" t="n">
-        <v>7.622222222222222</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="D31" t="n">
-        <v>7.75</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>6.5</v>
+        <v>4.238095238095238</v>
       </c>
       <c r="G31" t="n">
-        <v>5.972222222222222</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="H31" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I31" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02173913043478261</v>
+        <v>0.04545454545454546</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Der Schattenmacher</t>
+          <t>DIE DA OBEN!</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8.699999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="C32" t="n">
-        <v>8.318181818181818</v>
+        <v>1.85</v>
       </c>
       <c r="D32" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>3.611111111111111</v>
       </c>
       <c r="G32" t="n">
-        <v>6.666666666666667</v>
+        <v>2.055555555555555</v>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1513,270 +1493,270 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deutscher Bundestag</t>
+          <t>DIE WELTWOCHE</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.787931034482758</v>
+        <v>7.68157894736842</v>
       </c>
       <c r="C33" t="n">
-        <v>4.258620689655173</v>
+        <v>7.528947368421053</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>8.25</v>
       </c>
       <c r="E33" t="n">
-        <v>6.25</v>
+        <v>8.5</v>
       </c>
       <c r="F33" t="n">
-        <v>4.766666666666667</v>
+        <v>7.625714285714285</v>
       </c>
       <c r="G33" t="n">
-        <v>4.192982456140351</v>
+        <v>7.431428571428572</v>
       </c>
       <c r="H33" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="I33" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DeutscherHanfverband</t>
+          <t xml:space="preserve">DIE ZEIT </t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4.558823529411764</v>
+        <v>4.967741935483871</v>
       </c>
       <c r="C34" t="n">
-        <v>4.323529411764706</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="D34" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>4.433333333333334</v>
+        <v>4.966666666666667</v>
       </c>
       <c r="G34" t="n">
-        <v>4.4</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="H34" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>0.03125</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deutschland Kurier</t>
+          <t>DW Deutsch</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8.25</v>
+        <v>4.195652173913044</v>
       </c>
       <c r="C35" t="n">
-        <v>7.991379310344827</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="D35" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>8.364583333333334</v>
+        <v>4.195652173913044</v>
       </c>
       <c r="G35" t="n">
-        <v>8.166666666666666</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="H35" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.08</v>
       </c>
       <c r="J35" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Die Merkhilfe</t>
+          <t>Dekarldent</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>2.007317073170732</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>5.804878048780488</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>7.1875</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.08888888888888889</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5</v>
+        <v>0.08888888888888889</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DieLinke</t>
+          <t>Dennis und Benni Wolter</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.173913043478261</v>
+        <v>4.471428571428572</v>
       </c>
       <c r="C37" t="n">
-        <v>6.043478260869565</v>
+        <v>1.55</v>
       </c>
       <c r="D37" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1.173913043478261</v>
+        <v>4.325</v>
       </c>
       <c r="G37" t="n">
-        <v>6.043478260869565</v>
+        <v>2.071428571428572</v>
       </c>
       <c r="H37" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="I37" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.8679245283018868</v>
       </c>
       <c r="J37" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.8113207547169812</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EinfachSchule</t>
+          <t>Der Dunkle Parabelritter</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5.214285714285714</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>5.214285714285714</v>
+        <v>3.2</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3636363636363636</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3636363636363636</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">EndzeitreporterMcM </t>
+          <t>Der Medienfuzzi</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8.131578947368421</v>
+        <v>7.352272727272728</v>
       </c>
       <c r="C39" t="n">
-        <v>6.690476190476191</v>
+        <v>7.622222222222222</v>
       </c>
       <c r="D39" t="n">
-        <v>8.5</v>
+        <v>7.75</v>
       </c>
       <c r="E39" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
-        <v>8.03125</v>
+        <v>6.5</v>
       </c>
       <c r="G39" t="n">
-        <v>6.823529411764706</v>
+        <v>5.972222222222222</v>
       </c>
       <c r="H39" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.02173913043478261</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Erfolgskanal - Community für Finanzen &amp; Wirtschaft</t>
+          <t>Der Schattenmacher</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7.612903225806452</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>8.629032258064516</v>
+        <v>8.318181818181818</v>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="E40" t="n">
         <v>9</v>
       </c>
       <c r="F40" t="n">
-        <v>7.684210526315789</v>
+        <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>8.605263157894736</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -1785,274 +1765,286 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FOCUS online</t>
+          <t>Deutscher Bundestag</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5.195652173913044</v>
+        <v>4.787931034482758</v>
       </c>
       <c r="C41" t="n">
-        <v>1.521739130434783</v>
+        <v>4.258620689655173</v>
       </c>
       <c r="D41" t="n">
         <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="F41" t="n">
-        <v>5.272727272727272</v>
+        <v>4.766666666666667</v>
       </c>
       <c r="G41" t="n">
-        <v>1.590909090909091</v>
+        <v>4.192982456140351</v>
       </c>
       <c r="H41" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1481481481481481</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1481481481481481</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FinanzmarktWelt.de</t>
+          <t>DeutscherHanfverband</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6.276190476190477</v>
+        <v>4.558823529411764</v>
       </c>
       <c r="C42" t="n">
-        <v>4.340909090909091</v>
+        <v>4.323529411764706</v>
       </c>
       <c r="D42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E42" t="n">
         <v>6.5</v>
       </c>
-      <c r="E42" t="n">
-        <v>5</v>
-      </c>
       <c r="F42" t="n">
-        <v>6.276190476190477</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="G42" t="n">
-        <v>4.340909090909091</v>
+        <v>4.4</v>
       </c>
       <c r="H42" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Flavio von Witzleben</t>
+          <t>Deutschland Kurier</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7.078260869565218</v>
+        <v>8.25</v>
       </c>
       <c r="C43" t="n">
-        <v>8.456521739130435</v>
+        <v>7.991379310344827</v>
       </c>
       <c r="D43" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="E43" t="n">
         <v>8.5</v>
       </c>
       <c r="F43" t="n">
-        <v>7.078260869565218</v>
+        <v>8.364583333333334</v>
       </c>
       <c r="G43" t="n">
-        <v>8.456521739130435</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="H43" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Galileo</t>
+          <t>Die Merkhilfe</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4.735294117647059</v>
+        <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>4.735294117647059</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Geld für die Welt — Maurice Höfgen</t>
+          <t>DieLinke</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.3</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="C45" t="n">
-        <v>5.54</v>
+        <v>6.043478260869565</v>
       </c>
       <c r="D45" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E45" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="F45" t="n">
-        <v>2.4</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="G45" t="n">
-        <v>4.6</v>
+        <v>6.043478260869565</v>
       </c>
       <c r="H45" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>German Truck Driver</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+          <t>Digitaler Chronist</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>7.947058823529412</v>
+      </c>
+      <c r="C46" t="n">
+        <v>8.760784313725491</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9</v>
+      </c>
+      <c r="F46" t="n">
+        <v>7.778571428571429</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8.510714285714286</v>
+      </c>
       <c r="H46" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Gottfried Curio</t>
+          <t>Drewermann Kanal</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7.681818181818182</v>
+        <v>2.461538461538462</v>
       </c>
       <c r="C47" t="n">
-        <v>7.863636363636363</v>
+        <v>5.423076923076923</v>
       </c>
       <c r="D47" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="F47" t="n">
-        <v>7.681818181818182</v>
+        <v>2.541666666666667</v>
       </c>
       <c r="G47" t="n">
-        <v>7.863636363636363</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="H47" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.2777777777777778</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Hallo Meinung</t>
+          <t>EX - Rechte Rotlicht Rocker - Philip Schlaffer</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>8.282456140350877</v>
+        <v>3.878048780487805</v>
       </c>
       <c r="C48" t="n">
-        <v>8.814035087719297</v>
+        <v>1.855555555555556</v>
       </c>
       <c r="D48" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="F48" t="n">
-        <v>8.221951219512196</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
-        <v>8.717073170731707</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="H48" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I48" t="n">
-        <v>0.05</v>
+        <v>0.163265306122449</v>
       </c>
       <c r="J48" t="n">
-        <v>0.05</v>
+        <v>0.08163265306122448</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Handelsblatt</t>
+          <t>EinfachSchule</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5.482142857142857</v>
+        <v>5.214285714285714</v>
       </c>
       <c r="C49" t="n">
-        <v>1.321428571428571</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>5</v>
@@ -2061,118 +2053,118 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>5.5</v>
+        <v>5.214285714285714</v>
       </c>
       <c r="G49" t="n">
-        <v>1.092592592592593</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I49" t="n">
-        <v>0.03448275862068965</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="J49" t="n">
-        <v>0.03448275862068965</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Hessischer Rundfunk</t>
+          <t xml:space="preserve">EndzeitreporterMcM </t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4.481818181818181</v>
+        <v>8.131578947368421</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7272727272727273</v>
+        <v>6.690476190476191</v>
       </c>
       <c r="D50" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="F50" t="n">
-        <v>4.68</v>
+        <v>8.03125</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8</v>
+        <v>6.823529411764706</v>
       </c>
       <c r="H50" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.4615384615384616</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HeyWolfi</t>
+          <t>Energie &amp; Outdoor Chiemgau / Energie &amp; Vorsorge</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4.269230769230769</v>
+        <v>7.15483870967742</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>6.935483870967742</v>
       </c>
       <c r="D51" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="E51" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F51" t="n">
-        <v>3.818181818181818</v>
+        <v>7.263157894736842</v>
       </c>
       <c r="G51" t="n">
-        <v>3.45</v>
+        <v>6.789473684210527</v>
       </c>
       <c r="H51" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="I51" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08823529411764706</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.08823529411764706</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Horst Lüning (UnterBlog)</t>
+          <t>Erfolgskanal - Community für Finanzen &amp; Wirtschaft</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.583333333333333</v>
+        <v>7.612903225806452</v>
       </c>
       <c r="C52" t="n">
-        <v>7.75925925925926</v>
+        <v>8.629032258064516</v>
       </c>
       <c r="D52" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="F52" t="n">
-        <v>7.613636363636363</v>
+        <v>7.684210526315789</v>
       </c>
       <c r="G52" t="n">
-        <v>7.68</v>
+        <v>8.605263157894736</v>
       </c>
       <c r="H52" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2181,165 +2173,165 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jasmin Kosubek</t>
+          <t>FOCUS online</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>6.691666666666666</v>
+        <v>5.195652173913044</v>
       </c>
       <c r="C53" t="n">
-        <v>6.958333333333333</v>
+        <v>1.521739130434783</v>
       </c>
       <c r="D53" t="n">
-        <v>7.25</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>6.691666666666666</v>
+        <v>5.272727272727272</v>
       </c>
       <c r="G53" t="n">
-        <v>6.958333333333333</v>
+        <v>1.590909090909091</v>
       </c>
       <c r="H53" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.1481481481481481</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jung &amp; Naiv</t>
+          <t>FinanzmarktWelt.de</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3.5</v>
+        <v>6.276190476190477</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>4.340909090909091</v>
       </c>
       <c r="D54" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>3.5</v>
+        <v>6.276190476190477</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>4.340909090909091</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kettner-Edelmetalle (Gold &amp; Silber)</t>
+          <t>Flavio von Witzleben</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7.623728813559322</v>
+        <v>7.078260869565218</v>
       </c>
       <c r="C55" t="n">
-        <v>8.232203389830508</v>
+        <v>8.456521739130435</v>
       </c>
       <c r="D55" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="E55" t="n">
         <v>8.5</v>
       </c>
       <c r="F55" t="n">
-        <v>7.590566037735849</v>
+        <v>7.078260869565218</v>
       </c>
       <c r="G55" t="n">
-        <v>8.20188679245283</v>
+        <v>8.456521739130435</v>
       </c>
       <c r="H55" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="I55" t="n">
-        <v>0.01666666666666667</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.01666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kronen Zeitung</t>
+          <t>Florian Homm</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4.916666666666667</v>
+        <v>7.071428571428571</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9791666666666666</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="F56" t="n">
-        <v>4.977272727272728</v>
+        <v>7</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8863636363636364</v>
+        <v>8.384615384615385</v>
       </c>
       <c r="H56" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="J56" t="n">
-        <v>0.4146341463414634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Küppersbusch TV</t>
+          <t>Florian Schroeder</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4.324324324324325</v>
+        <v>3.923076923076923</v>
       </c>
       <c r="C57" t="n">
-        <v>3.594594594594595</v>
+        <v>4.923076923076923</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="F57" t="n">
-        <v>4.257142857142857</v>
+        <v>3.923076923076923</v>
       </c>
       <c r="G57" t="n">
-        <v>3.3</v>
+        <v>4.923076923076923</v>
       </c>
       <c r="H57" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -2351,29 +2343,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LEO – Ketzer der Neuzeit</t>
+          <t>Frei &amp; Unbeugsam</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>8.111111111111111</v>
+        <v>8.108695652173912</v>
       </c>
       <c r="C58" t="n">
-        <v>8.555555555555555</v>
+        <v>8.826086956521738</v>
       </c>
       <c r="D58" t="n">
         <v>8.5</v>
       </c>
       <c r="E58" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>7.75</v>
+        <v>8.03448275862069</v>
       </c>
       <c r="G58" t="n">
-        <v>8</v>
+        <v>8.706896551724139</v>
       </c>
       <c r="H58" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -2385,703 +2377,731 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Landwirtschaft erLEEben mit Anthony Lee</t>
+          <t>GabbaGandalfTV</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7.653846153846154</v>
+        <v>7.826086956521739</v>
       </c>
       <c r="C59" t="n">
-        <v>8.5</v>
+        <v>7.510869565217392</v>
       </c>
       <c r="D59" t="n">
         <v>7.5</v>
       </c>
       <c r="E59" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="F59" t="n">
         <v>7.75</v>
       </c>
       <c r="G59" t="n">
-        <v>8.5625</v>
+        <v>6.625</v>
       </c>
       <c r="H59" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Langemann Medien</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+          <t>Galileo</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>4.735294117647059</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4.735294117647059</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.333333333333333</v>
+      </c>
       <c r="H60" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MDR Investigativ</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+          <t>Geld für die Welt — Maurice Höfgen</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C61" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4.6</v>
+      </c>
       <c r="H61" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MDR Mitteldeutscher Rundfunk</t>
+          <t>Gerald Grosz</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>8.691666666666666</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>7.192307692307693</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>8.663461538461538</v>
       </c>
       <c r="H62" t="n">
         <v>60</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9666666666666667</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0.9666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mario Lochner</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>6.773529411764706</v>
-      </c>
-      <c r="C63" t="n">
-        <v>4.597222222222222</v>
-      </c>
-      <c r="D63" t="n">
-        <v>7</v>
-      </c>
-      <c r="E63" t="n">
-        <v>6</v>
-      </c>
-      <c r="F63" t="n">
-        <v>6.751515151515152</v>
-      </c>
-      <c r="G63" t="n">
-        <v>4.528571428571428</v>
-      </c>
+          <t>German Truck Driver</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2916666666666667</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Martin Lejeune</t>
+          <t>Gottfried Curio</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4.705882352941177</v>
+        <v>7.681818181818182</v>
       </c>
       <c r="C64" t="n">
-        <v>1.941176470588235</v>
+        <v>7.863636363636363</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="F64" t="n">
-        <v>4.705882352941177</v>
+        <v>7.681818181818182</v>
       </c>
       <c r="G64" t="n">
-        <v>1.941176470588235</v>
+        <v>7.863636363636363</v>
       </c>
       <c r="H64" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6530612244897959</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.6530612244897959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Marvin Neumann</t>
+          <t>Grenzgänger Studios</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4.96875</v>
+        <v>5.9375</v>
       </c>
       <c r="C65" t="n">
-        <v>0.28125</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>7.875</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H65" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Massengeschmack-TV</t>
+          <t>HABITAT - Lebensraum Deutschland</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5.375</v>
+        <v>7.338596491228071</v>
       </c>
       <c r="C66" t="n">
-        <v>5.375</v>
+        <v>7.211864406779661</v>
       </c>
       <c r="D66" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="E66" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F66" t="n">
-        <v>5.75</v>
+        <v>7.302564102564103</v>
       </c>
       <c r="G66" t="n">
-        <v>4.875</v>
+        <v>6.9625</v>
       </c>
       <c r="H66" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>0.03389830508474576</v>
       </c>
       <c r="J66" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Monitor</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+          <t>Hallo Meinung</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>8.282456140350877</v>
+      </c>
+      <c r="C67" t="n">
+        <v>8.814035087719297</v>
+      </c>
+      <c r="D67" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E67" t="n">
+        <v>9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>8.221951219512196</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8.717073170731707</v>
+      </c>
       <c r="H67" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NachDenkSeiten</t>
+          <t>Handelsblatt</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4.232</v>
+        <v>5.482142857142857</v>
       </c>
       <c r="C68" t="n">
-        <v>7.3</v>
+        <v>1.321428571428571</v>
       </c>
       <c r="D68" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>4.295652173913044</v>
+        <v>5.5</v>
       </c>
       <c r="G68" t="n">
-        <v>7.195652173913044</v>
+        <v>1.092592592592593</v>
       </c>
       <c r="H68" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>0.03448275862068965</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>0.03448275862068965</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OE24.TV</t>
+          <t>Hessischer Rundfunk</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5.332142857142857</v>
+        <v>4.481818181818181</v>
       </c>
       <c r="C69" t="n">
-        <v>4.035714285714286</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="E69" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>5.437037037037038</v>
+        <v>4.68</v>
       </c>
       <c r="G69" t="n">
-        <v>4.185185185185185</v>
+        <v>0.8</v>
       </c>
       <c r="H69" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="I69" t="n">
-        <v>0.03448275862068965</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="J69" t="n">
-        <v>0.03448275862068965</v>
+        <v>0.8166666666666667</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Oli</t>
+          <t>HeyWolfi</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>7.416666666666667</v>
+        <v>4.269230769230769</v>
       </c>
       <c r="C70" t="n">
-        <v>7.741666666666666</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="E70" t="n">
-        <v>8.25</v>
+        <v>3.5</v>
       </c>
       <c r="F70" t="n">
-        <v>7.34375</v>
+        <v>3.818181818181818</v>
       </c>
       <c r="G70" t="n">
-        <v>7.453125</v>
+        <v>3.45</v>
       </c>
       <c r="H70" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Oli investiert</t>
+          <t>Hiphop.de</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>7.368333333333334</v>
+        <v>3.916666666666667</v>
       </c>
       <c r="C71" t="n">
-        <v>7.903333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="D71" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="F71" t="n">
-        <v>7.278571428571429</v>
+        <v>3.916666666666667</v>
       </c>
       <c r="G71" t="n">
-        <v>7.678571428571429</v>
+        <v>1.5</v>
       </c>
       <c r="H71" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Oli redet</t>
+          <t>Horst Lüning (UnterBlog)</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>6.842307692307693</v>
+        <v>7.583333333333333</v>
       </c>
       <c r="C72" t="n">
-        <v>6.481818181818181</v>
+        <v>7.75925925925926</v>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="F72" t="n">
-        <v>6.772727272727272</v>
+        <v>7.613636363636363</v>
       </c>
       <c r="G72" t="n">
-        <v>5.645833333333333</v>
+        <v>7.68</v>
       </c>
       <c r="H72" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I72" t="n">
-        <v>0.103448275862069</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="J72" t="n">
-        <v>0.05172413793103448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">POLITIK SPEZIAL - Stimme der Vernunft </t>
+          <t>InfoBox</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>7.642857142857143</v>
+        <v>8.105263157894736</v>
       </c>
       <c r="C73" t="n">
-        <v>8.017241379310345</v>
+        <v>9.052631578947368</v>
       </c>
       <c r="D73" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="F73" t="n">
-        <v>7.76</v>
+        <v>7.6875</v>
       </c>
       <c r="G73" t="n">
-        <v>7.923076923076923</v>
+        <v>9.1875</v>
       </c>
       <c r="H73" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I73" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.05</v>
       </c>
       <c r="J73" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Peter Boehringer</t>
+          <t>InfraRot - dein Durchblick im Nachrichtennebel</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>8.315789473684211</v>
+        <v>7.770833333333333</v>
       </c>
       <c r="C74" t="n">
-        <v>8.815789473684211</v>
+        <v>8.96875</v>
       </c>
       <c r="D74" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="E74" t="n">
         <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>8.5</v>
+        <v>7.772727272727272</v>
       </c>
       <c r="G74" t="n">
-        <v>8.73076923076923</v>
+        <v>8.939393939393939</v>
       </c>
       <c r="H74" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1272727272727273</v>
       </c>
       <c r="J74" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1272727272727273</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Peter Weber</t>
+          <t>Investinbest</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>8.1</v>
+        <v>7.907843137254902</v>
       </c>
       <c r="C75" t="n">
-        <v>8.753448275862068</v>
+        <v>8.770588235294118</v>
       </c>
       <c r="D75" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="E75" t="n">
         <v>9</v>
       </c>
       <c r="F75" t="n">
-        <v>8.133333333333333</v>
+        <v>7.836585365853659</v>
       </c>
       <c r="G75" t="n">
-        <v>8.709803921568627</v>
+        <v>8.714634146341464</v>
       </c>
       <c r="H75" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I75" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03773584905660377</v>
       </c>
       <c r="J75" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03773584905660377</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Politik &amp; Co </t>
+          <t>Jasmin Kosubek</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6.833333333333333</v>
+        <v>6.691666666666666</v>
       </c>
       <c r="C76" t="n">
-        <v>7.666666666666667</v>
+        <v>6.958333333333333</v>
       </c>
       <c r="D76" t="n">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="E76" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+        <v>7.75</v>
+      </c>
+      <c r="F76" t="n">
+        <v>6.691666666666666</v>
+      </c>
+      <c r="G76" t="n">
+        <v>6.958333333333333</v>
+      </c>
       <c r="H76" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>REALTALK MEDIA</t>
+          <t>Jung &amp; Naiv</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>5.625</v>
+        <v>3.5</v>
       </c>
       <c r="C77" t="n">
-        <v>8.1875</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="E77" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>5.214285714285714</v>
+        <v>3.5</v>
       </c>
       <c r="G77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RTL Aktuell</t>
+          <t>Kai Brenner - Per Du mit dem Leben 😃</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5.133333333333334</v>
+        <v>6.842105263157895</v>
       </c>
       <c r="C78" t="n">
-        <v>1.258064516129032</v>
+        <v>8.226415094339623</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="F78" t="n">
-        <v>5.189655172413793</v>
+        <v>6.578947368421052</v>
       </c>
       <c r="G78" t="n">
-        <v>1.3</v>
+        <v>8.018518518518519</v>
       </c>
       <c r="H78" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="J78" t="n">
-        <v>0.1621621621621622</v>
+        <v>0.01851851851851852</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RTV Privatfernsehen</t>
+          <t>Kettner-Edelmetalle (Gold &amp; Silber)</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7.195652173913044</v>
+        <v>7.623728813559322</v>
       </c>
       <c r="C79" t="n">
-        <v>6.586956521739131</v>
+        <v>8.232203389830508</v>
       </c>
       <c r="D79" t="n">
         <v>7.5</v>
       </c>
       <c r="E79" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="F79" t="n">
-        <v>7.204545454545454</v>
+        <v>7.590566037735849</v>
       </c>
       <c r="G79" t="n">
-        <v>6.613636363636363</v>
+        <v>8.20188679245283</v>
       </c>
       <c r="H79" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Red Scorpion</t>
+          <t>Kontraste - Der Wirtschaftsblog</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4.777777777777778</v>
+        <v>8.272727272727273</v>
       </c>
       <c r="C80" t="n">
-        <v>8.333333333333334</v>
+        <v>8.659090909090908</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="F80" t="n">
-        <v>4.833333333333333</v>
+        <v>8.40625</v>
       </c>
       <c r="G80" t="n">
-        <v>7</v>
+        <v>8.8125</v>
       </c>
       <c r="H80" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -3093,221 +3113,221 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Roger Beckamp</t>
+          <t>Krabbe</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>7.916666666666667</v>
+        <v>7.368421052631579</v>
       </c>
       <c r="C81" t="n">
-        <v>7.895833333333333</v>
+        <v>3.894736842105263</v>
       </c>
       <c r="D81" t="n">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="E81" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="F81" t="n">
-        <v>7.928571428571429</v>
+        <v>7.388888888888889</v>
       </c>
       <c r="G81" t="n">
-        <v>7.928571428571429</v>
+        <v>3.638888888888889</v>
       </c>
       <c r="H81" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="J81" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.5777777777777777</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Russische Welt TV</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="C82" t="n">
-        <v>7.722222222222222</v>
-      </c>
-      <c r="D82" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E82" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F82" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G82" t="n">
-        <v>7.5625</v>
-      </c>
+          <t>Krissy Rieger</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SPACE FROGS</t>
+          <t>Kronen Zeitung</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4.25</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="C83" t="n">
-        <v>4.133333333333334</v>
+        <v>0.9791666666666666</v>
       </c>
       <c r="D83" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>4.1875</v>
+        <v>4.977272727272728</v>
       </c>
       <c r="G83" t="n">
-        <v>4.05</v>
+        <v>0.8863636363636364</v>
       </c>
       <c r="H83" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="J83" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.4146341463414634</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SRF Comedy</t>
+          <t>Krypto Report</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>5.111111111111111</v>
+        <v>7</v>
       </c>
       <c r="C84" t="n">
-        <v>3.277777777777778</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E84" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="F84" t="n">
-        <v>5.125</v>
+        <v>7</v>
       </c>
       <c r="G84" t="n">
-        <v>3.6875</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="H84" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="J84" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SRF Kids</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
+          <t>KuchenTV</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="D85" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4.625</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3.875</v>
+      </c>
       <c r="H85" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>0.4680851063829787</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0.3617021276595745</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SWR</t>
+          <t>Küppersbusch TV</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5.32093023255814</v>
+        <v>4.324324324324325</v>
       </c>
       <c r="C86" t="n">
-        <v>2.579545454545455</v>
+        <v>3.594594594594595</v>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>5.364285714285715</v>
+        <v>4.257142857142857</v>
       </c>
       <c r="G86" t="n">
-        <v>2.616279069767442</v>
+        <v>3.3</v>
       </c>
       <c r="H86" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2181818181818182</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sahra Wagenknecht</t>
+          <t>LEO – Ketzer der Neuzeit</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5.833333333333333</v>
+        <v>8.111111111111111</v>
       </c>
       <c r="C87" t="n">
-        <v>8.166666666666666</v>
+        <v>8.555555555555555</v>
       </c>
       <c r="D87" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="E87" t="n">
         <v>8.5</v>
       </c>
       <c r="F87" t="n">
-        <v>5.833333333333333</v>
+        <v>7.75</v>
       </c>
       <c r="G87" t="n">
-        <v>8.166666666666666</v>
+        <v>8</v>
       </c>
       <c r="H87" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -3319,29 +3339,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SchrangTV</t>
+          <t>Landwirtschaft erLEEben mit Anthony Lee</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>7.466666666666667</v>
+        <v>7.653846153846154</v>
       </c>
       <c r="C88" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="D88" t="n">
         <v>7.5</v>
       </c>
       <c r="E88" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="F88" t="n">
-        <v>7.346153846153846</v>
+        <v>7.75</v>
       </c>
       <c r="G88" t="n">
-        <v>8.5</v>
+        <v>8.5625</v>
       </c>
       <c r="H88" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -3353,496 +3373,472 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Schuler! Fragen, was ist</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>7.161290322580645</v>
-      </c>
-      <c r="C89" t="n">
-        <v>5.145161290322581</v>
-      </c>
-      <c r="D89" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E89" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F89" t="n">
-        <v>7.172413793103448</v>
-      </c>
-      <c r="G89" t="n">
-        <v>5.137931034482759</v>
-      </c>
+          <t>Langemann Medien</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ServusTV On</t>
+          <t>LeFloid</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>6.236842105263158</v>
+        <v>4.909090909090909</v>
       </c>
       <c r="C90" t="n">
-        <v>5.947368421052632</v>
+        <v>4.363636363636363</v>
       </c>
       <c r="D90" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="F90" t="n">
-        <v>6.236842105263158</v>
+        <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>5.947368421052632</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="H90" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I90" t="n">
-        <v>0.24</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J90" t="n">
-        <v>0.24</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Staiy</t>
+          <t>Leon Lovelock</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3.525</v>
+        <v>7.25</v>
       </c>
       <c r="C91" t="n">
-        <v>3.260416666666667</v>
+        <v>8.75</v>
       </c>
       <c r="D91" t="n">
-        <v>3.5</v>
+        <v>7.25</v>
       </c>
       <c r="E91" t="n">
-        <v>1.5</v>
+        <v>8.75</v>
       </c>
       <c r="F91" t="n">
-        <v>3.9</v>
+        <v>7.25</v>
       </c>
       <c r="G91" t="n">
-        <v>3.2</v>
+        <v>8.75</v>
       </c>
       <c r="H91" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3220338983050847</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0.1864406779661017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Stephan Brandner, AfD</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>7.483333333333333</v>
-      </c>
-      <c r="C92" t="n">
-        <v>6.845238095238095</v>
-      </c>
-      <c r="D92" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E92" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F92" t="n">
-        <v>7.483333333333333</v>
-      </c>
-      <c r="G92" t="n">
-        <v>6.845238095238095</v>
-      </c>
+          <t>MDR Investigativ</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="I92" t="n">
-        <v>0.02325581395348837</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>0.02325581395348837</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Steuern mit Kopf</t>
+          <t>MDR Mitteldeutscher Rundfunk</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>6.604651162790698</v>
+        <v>5</v>
       </c>
       <c r="C93" t="n">
-        <v>4.111111111111111</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
-        <v>6.604651162790698</v>
+        <v>5</v>
       </c>
       <c r="G93" t="n">
-        <v>4.111111111111111</v>
+        <v>3</v>
       </c>
       <c r="H93" t="n">
         <v>60</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J93" t="n">
-        <v>0.25</v>
+        <v>0.9666666666666667</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Stuttgarter Zeitung &amp; Stuttgarter Nachrichten</t>
+          <t>MMnewsTV</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4.875</v>
+        <v>7.635135135135135</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>8.175675675675675</v>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="F94" t="n">
-        <v>4.875</v>
+        <v>7.574074074074074</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>7.944444444444445</v>
       </c>
       <c r="H94" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>0.1590909090909091</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>0.1590909090909091</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tagesspiegel</t>
+          <t>Mario Lochner</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>5</v>
+        <v>6.773529411764706</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3333333333333333</v>
+        <v>4.597222222222222</v>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F95" t="n">
-        <v>5</v>
+        <v>6.751515151515152</v>
       </c>
       <c r="G95" t="n">
-        <v>0.5</v>
+        <v>4.528571428571428</v>
       </c>
       <c r="H95" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="J95" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tichys Einblick</t>
+          <t>Martin Lejeune</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>7.526315789473684</v>
+        <v>4.705882352941177</v>
       </c>
       <c r="C96" t="n">
-        <v>7.289473684210527</v>
+        <v>1.941176470588235</v>
       </c>
       <c r="D96" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E96" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>7.526315789473684</v>
+        <v>4.705882352941177</v>
       </c>
       <c r="G96" t="n">
-        <v>7.289473684210527</v>
+        <v>1.941176470588235</v>
       </c>
       <c r="H96" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>0.6530612244897959</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>0.6530612244897959</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tobias Huch</t>
+          <t>Marvin Neumann</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4.674074074074074</v>
+        <v>4.96875</v>
       </c>
       <c r="C97" t="n">
-        <v>4.333333333333333</v>
+        <v>0.28125</v>
       </c>
       <c r="D97" t="n">
         <v>5</v>
       </c>
       <c r="E97" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VisualPolitik DE</t>
+          <t>Massengeschmack-TV</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5.3</v>
+        <v>5.375</v>
       </c>
       <c r="C98" t="n">
-        <v>2.48</v>
+        <v>5.375</v>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F98" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="G98" t="n">
-        <v>2.48</v>
+        <v>4.875</v>
       </c>
       <c r="H98" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>WBS LEGAL</t>
+          <t>Mathias von Gersdorff</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>4.76</v>
+        <v>7.754385964912281</v>
       </c>
       <c r="C99" t="n">
-        <v>1.378787878787879</v>
+        <v>7.137931034482759</v>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="F99" t="n">
-        <v>4.795454545454546</v>
+        <v>7.642857142857143</v>
       </c>
       <c r="G99" t="n">
-        <v>1.327586206896552</v>
+        <v>6.706896551724138</v>
       </c>
       <c r="H99" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I99" t="n">
-        <v>0.375</v>
+        <v>0.05</v>
       </c>
       <c r="J99" t="n">
-        <v>0.175</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>WDR aktuell</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+          <t>Maximilian Pütz</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>8.032142857142857</v>
+      </c>
+      <c r="C100" t="n">
+        <v>8.525862068965518</v>
+      </c>
+      <c r="D100" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E100" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F100" t="n">
+        <v>7.6875</v>
+      </c>
+      <c r="G100" t="n">
+        <v>8.375</v>
+      </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="J100" t="n">
-        <v>1</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>WELT Netzreporter</t>
+          <t>Mission Money</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5.347826086956522</v>
+        <v>6.7</v>
       </c>
       <c r="C101" t="n">
-        <v>1.108695652173913</v>
+        <v>3.0625</v>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F101" t="n">
-        <v>5.347826086956522</v>
+        <v>6.7</v>
       </c>
       <c r="G101" t="n">
-        <v>1.108695652173913</v>
+        <v>3.0625</v>
       </c>
       <c r="H101" t="n">
         <v>23</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Weichreite TV</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>7.140625</v>
-      </c>
-      <c r="C102" t="n">
-        <v>6.621212121212121</v>
-      </c>
-      <c r="D102" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E102" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F102" t="n">
-        <v>7.25925925925926</v>
-      </c>
-      <c r="G102" t="n">
-        <v>7.462962962962963</v>
-      </c>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4666666666666667</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ZDF heute-show</t>
+          <t>NachDenkSeiten</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>4.431818181818182</v>
+        <v>4.232</v>
       </c>
       <c r="C103" t="n">
-        <v>4.3125</v>
+        <v>7.3</v>
       </c>
       <c r="D103" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="E103" t="n">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="F103" t="n">
-        <v>4.425</v>
+        <v>4.295652173913044</v>
       </c>
       <c r="G103" t="n">
-        <v>4.238095238095238</v>
+        <v>7.195652173913044</v>
       </c>
       <c r="H103" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I103" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -3851,97 +3847,97 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ZDFheute Nachrichten</t>
+          <t>Nuoviso Files</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5.04</v>
+        <v>6.75</v>
       </c>
       <c r="C104" t="n">
-        <v>1.64</v>
+        <v>6.142857142857143</v>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="F104" t="n">
-        <v>4.958333333333333</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G104" t="n">
-        <v>1.708333333333333</v>
+        <v>5.583333333333333</v>
       </c>
       <c r="H104" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ZDFtivi</t>
+          <t>OE24.TV</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>4.769230769230769</v>
+        <v>5.332142857142857</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>4.035714285714286</v>
       </c>
       <c r="D105" t="n">
         <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="F105" t="n">
-        <v>4.769230769230769</v>
+        <v>5.437037037037038</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>4.185185185185185</v>
       </c>
       <c r="H105" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I105" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.03448275862068965</v>
       </c>
       <c r="J105" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.03448275862068965</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>_horizont_</t>
+          <t>Oli</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5.615384615384615</v>
+        <v>7.416666666666667</v>
       </c>
       <c r="C106" t="n">
-        <v>3.115384615384615</v>
+        <v>7.741666666666666</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>8.25</v>
       </c>
       <c r="F106" t="n">
-        <v>5.25</v>
+        <v>7.34375</v>
       </c>
       <c r="G106" t="n">
-        <v>3.25</v>
+        <v>7.453125</v>
       </c>
       <c r="H106" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
@@ -3953,29 +3949,29 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>acTVism Munich</t>
+          <t>Oli investiert</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>7.5</v>
+        <v>7.368333333333334</v>
       </c>
       <c r="C107" t="n">
-        <v>8.5</v>
+        <v>7.903333333333333</v>
       </c>
       <c r="D107" t="n">
         <v>7.5</v>
       </c>
       <c r="E107" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="F107" t="n">
-        <v>7.5</v>
+        <v>7.278571428571429</v>
       </c>
       <c r="G107" t="n">
-        <v>8.5</v>
+        <v>7.678571428571429</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
@@ -3987,341 +3983,2025 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>congstar</t>
+          <t>Oli redet</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3</v>
+        <v>6.842307692307693</v>
       </c>
       <c r="C108" t="n">
-        <v>0.25</v>
+        <v>6.481818181818181</v>
       </c>
       <c r="D108" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>6.772727272727272</v>
       </c>
       <c r="G108" t="n">
-        <v>0.25</v>
+        <v>5.645833333333333</v>
       </c>
       <c r="H108" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="J108" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.05172413793103448</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>euronews (deutsch)</t>
+          <t xml:space="preserve">POLITIK SPEZIAL - Stimme der Vernunft </t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5</v>
+        <v>7.642857142857143</v>
       </c>
       <c r="C109" t="n">
-        <v>0.08</v>
+        <v>8.017241379310345</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F109" t="n">
-        <v>5</v>
+        <v>7.76</v>
       </c>
       <c r="G109" t="n">
-        <v>0.08</v>
+        <v>7.923076923076923</v>
       </c>
       <c r="H109" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4318181818181818</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="J109" t="n">
-        <v>0.4318181818181818</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>extra 3</t>
+          <t>Peter Boehringer</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>4</v>
+        <v>8.315789473684211</v>
       </c>
       <c r="C110" t="n">
-        <v>3.963414634146341</v>
+        <v>8.815789473684211</v>
       </c>
       <c r="D110" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="E110" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="F110" t="n">
-        <v>4.073529411764706</v>
+        <v>8.5</v>
       </c>
       <c r="G110" t="n">
-        <v>3.986111111111111</v>
+        <v>8.73076923076923</v>
       </c>
       <c r="H110" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="I110" t="n">
-        <v>0.35</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="J110" t="n">
-        <v>0.3166666666666667</v>
+        <v>0.1363636363636364</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>faz</t>
+          <t>Peter Weber</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>4.793103448275862</v>
+        <v>8.1</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1206896551724138</v>
+        <v>8.753448275862068</v>
       </c>
       <c r="D111" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F111" t="n">
-        <v>4.785714285714286</v>
+        <v>8.133333333333333</v>
       </c>
       <c r="G111" t="n">
-        <v>0.125</v>
+        <v>8.709803921568627</v>
       </c>
       <c r="H111" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="I111" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="J111" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>hessenschau</t>
+          <t xml:space="preserve">Politik &amp; Co </t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>4.666666666666667</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
+        <v>8.5</v>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>phoenix</t>
+          <t>Prinz</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>4.574193548387097</v>
+        <v>3.772727272727273</v>
       </c>
       <c r="C113" t="n">
-        <v>2.032258064516129</v>
+        <v>2.791666666666667</v>
       </c>
       <c r="D113" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="F113" t="n">
-        <v>4.596551724137932</v>
+        <v>3</v>
       </c>
       <c r="G113" t="n">
-        <v>2.172413793103448</v>
+        <v>0.5</v>
       </c>
       <c r="H113" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I113" t="n">
-        <v>0.03125</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="J113" t="n">
-        <v>0.03125</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>stern TV</t>
+          <t>Punkt.PRERADOVIC</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>4.522727272727272</v>
+        <v>7.038461538461538</v>
       </c>
       <c r="C114" t="n">
-        <v>1.434782608695652</v>
+        <v>8.538461538461538</v>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="F114" t="n">
-        <v>4.522727272727272</v>
+        <v>6.6</v>
       </c>
       <c r="G114" t="n">
-        <v>1.434782608695652</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4054054054054054</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>0.3783783783783784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>taff</t>
+          <t>QS24 - Schweizer Gesundheitsfernsehen</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>4.5</v>
+        <v>5.95</v>
       </c>
       <c r="C115" t="n">
-        <v>0.3888888888888889</v>
+        <v>5.368421052631579</v>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="F115" t="n">
-        <v>4.5</v>
+        <v>5.95</v>
       </c>
       <c r="G115" t="n">
-        <v>0.3888888888888889</v>
+        <v>5.368421052631579</v>
       </c>
       <c r="H115" t="n">
         <v>60</v>
       </c>
       <c r="I115" t="n">
-        <v>0.85</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J115" t="n">
-        <v>0.85</v>
+        <v>0.3666666666666666</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>tagesschau</t>
+          <t>REALTALK MEDIA</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>4.744444444444444</v>
+        <v>5.625</v>
       </c>
       <c r="C116" t="n">
-        <v>0.3513513513513514</v>
+        <v>8.1875</v>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="F116" t="n">
-        <v>4.744444444444444</v>
+        <v>5.214285714285714</v>
       </c>
       <c r="G116" t="n">
-        <v>0.3513513513513514</v>
+        <v>8</v>
       </c>
       <c r="H116" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="I116" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="J116" t="n">
-        <v>0.05128205128205128</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>ROOZ WORLD</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>4.423076923076923</v>
+      </c>
+      <c r="C117" t="n">
+        <v>4.977272727272728</v>
+      </c>
+      <c r="D117" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" t="n">
+        <v>7</v>
+      </c>
+      <c r="F117" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G117" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="H117" t="n">
+        <v>58</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.7758620689655172</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.6206896551724138</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>RTL Aktuell</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>5.133333333333334</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.258064516129032</v>
+      </c>
+      <c r="D118" t="n">
+        <v>5</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>5.189655172413793</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H118" t="n">
+        <v>37</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.1891891891891892</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>RTV Privatfernsehen</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>7.195652173913044</v>
+      </c>
+      <c r="C119" t="n">
+        <v>6.586956521739131</v>
+      </c>
+      <c r="D119" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E119" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F119" t="n">
+        <v>7.204545454545454</v>
+      </c>
+      <c r="G119" t="n">
+        <v>6.613636363636363</v>
+      </c>
+      <c r="H119" t="n">
+        <v>23</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Red Scorpion</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>4.777777777777778</v>
+      </c>
+      <c r="C120" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="D120" t="n">
+        <v>5</v>
+      </c>
+      <c r="E120" t="n">
+        <v>9</v>
+      </c>
+      <c r="F120" t="n">
+        <v>4.833333333333333</v>
+      </c>
+      <c r="G120" t="n">
+        <v>7</v>
+      </c>
+      <c r="H120" t="n">
+        <v>9</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Roger Beckamp</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>7.916666666666667</v>
+      </c>
+      <c r="C121" t="n">
+        <v>7.895833333333333</v>
+      </c>
+      <c r="D121" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E121" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F121" t="n">
+        <v>7.928571428571429</v>
+      </c>
+      <c r="G121" t="n">
+        <v>7.928571428571429</v>
+      </c>
+      <c r="H121" t="n">
+        <v>27</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Russische Welt TV</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C122" t="n">
+        <v>7.722222222222222</v>
+      </c>
+      <c r="D122" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E122" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F122" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G122" t="n">
+        <v>7.5625</v>
+      </c>
+      <c r="H122" t="n">
+        <v>10</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SPACE FROGS</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C123" t="n">
+        <v>4.133333333333334</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E123" t="n">
+        <v>4</v>
+      </c>
+      <c r="F123" t="n">
+        <v>4.1875</v>
+      </c>
+      <c r="G123" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H123" t="n">
+        <v>18</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SRF Comedy</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>5.111111111111111</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3.277777777777778</v>
+      </c>
+      <c r="D124" t="n">
+        <v>5</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F124" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="G124" t="n">
+        <v>3.6875</v>
+      </c>
+      <c r="H124" t="n">
+        <v>31</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SWR</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>5.32093023255814</v>
+      </c>
+      <c r="C125" t="n">
+        <v>2.579545454545455</v>
+      </c>
+      <c r="D125" t="n">
+        <v>5</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>5.364285714285715</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2.616279069767442</v>
+      </c>
+      <c r="H125" t="n">
+        <v>55</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.2181818181818182</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Sahra Wagenknecht</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="C126" t="n">
+        <v>8.166666666666666</v>
+      </c>
+      <c r="D126" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E126" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F126" t="n">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="G126" t="n">
+        <v>8.166666666666666</v>
+      </c>
+      <c r="H126" t="n">
+        <v>3</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SchrangTV</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>7.466666666666667</v>
+      </c>
+      <c r="C127" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D127" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E127" t="n">
+        <v>9</v>
+      </c>
+      <c r="F127" t="n">
+        <v>7.346153846153846</v>
+      </c>
+      <c r="G127" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H127" t="n">
+        <v>15</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Schuler! Fragen, was ist</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>7.161290322580645</v>
+      </c>
+      <c r="C128" t="n">
+        <v>5.145161290322581</v>
+      </c>
+      <c r="D128" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E128" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F128" t="n">
+        <v>7.172413793103448</v>
+      </c>
+      <c r="G128" t="n">
+        <v>5.137931034482759</v>
+      </c>
+      <c r="H128" t="n">
+        <v>31</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ServusTV On</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>6.236842105263158</v>
+      </c>
+      <c r="C129" t="n">
+        <v>5.947368421052632</v>
+      </c>
+      <c r="D129" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E129" t="n">
+        <v>7</v>
+      </c>
+      <c r="F129" t="n">
+        <v>6.236842105263158</v>
+      </c>
+      <c r="G129" t="n">
+        <v>5.947368421052632</v>
+      </c>
+      <c r="H129" t="n">
+        <v>25</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Staiy</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="H130" t="n">
+        <v>76</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3421052631578947</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.2236842105263158</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Stephan Brandner, AfD</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>7.483333333333333</v>
+      </c>
+      <c r="C131" t="n">
+        <v>6.845238095238095</v>
+      </c>
+      <c r="D131" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E131" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F131" t="n">
+        <v>7.483333333333333</v>
+      </c>
+      <c r="G131" t="n">
+        <v>6.845238095238095</v>
+      </c>
+      <c r="H131" t="n">
+        <v>43</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.02325581395348837</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.02325581395348837</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Steuern mit Kopf</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>6.604651162790698</v>
+      </c>
+      <c r="C132" t="n">
+        <v>4.111111111111111</v>
+      </c>
+      <c r="D132" t="n">
+        <v>7</v>
+      </c>
+      <c r="E132" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F132" t="n">
+        <v>6.604651162790698</v>
+      </c>
+      <c r="G132" t="n">
+        <v>4.111111111111111</v>
+      </c>
+      <c r="H132" t="n">
+        <v>60</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Stuttgarter Zeitung &amp; Stuttgarter Nachrichten</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>5</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>8</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Tagesspiegel</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>5</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D134" t="n">
+        <v>5</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H134" t="n">
+        <v>5</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Tichys Einblick</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>7.526315789473684</v>
+      </c>
+      <c r="C135" t="n">
+        <v>7.289473684210527</v>
+      </c>
+      <c r="D135" t="n">
+        <v>8</v>
+      </c>
+      <c r="E135" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F135" t="n">
+        <v>7.526315789473684</v>
+      </c>
+      <c r="G135" t="n">
+        <v>7.289473684210527</v>
+      </c>
+      <c r="H135" t="n">
+        <v>19</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Tobias Huch</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>4.674074074074074</v>
+      </c>
+      <c r="C136" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="D136" t="n">
+        <v>5</v>
+      </c>
+      <c r="E136" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F136" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" t="n">
+        <v>28</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>VisualPolitik DE</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="D137" t="n">
+        <v>5</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H137" t="n">
+        <v>25</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>WBS LEGAL</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.378787878787879</v>
+      </c>
+      <c r="D138" t="n">
+        <v>5</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>4.795454545454546</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1.327586206896552</v>
+      </c>
+      <c r="H138" t="n">
+        <v>40</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>WDR aktuell</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>WELT Netzreporter</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>5.347826086956522</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1.108695652173913</v>
+      </c>
+      <c r="D140" t="n">
+        <v>5</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>5.347826086956522</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1.108695652173913</v>
+      </c>
+      <c r="H140" t="n">
+        <v>23</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Weichreite TV</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C141" t="n">
+        <v>6.25609756097561</v>
+      </c>
+      <c r="D141" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E141" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F141" t="n">
+        <v>6.957142857142857</v>
+      </c>
+      <c r="G141" t="n">
+        <v>6.842857142857143</v>
+      </c>
+      <c r="H141" t="n">
+        <v>75</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.4533333333333333</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Westend Verlag</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>5.145833333333333</v>
+      </c>
+      <c r="C142" t="n">
+        <v>5.479166666666667</v>
+      </c>
+      <c r="D142" t="n">
+        <v>5</v>
+      </c>
+      <c r="E142" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F142" t="n">
+        <v>5.145833333333333</v>
+      </c>
+      <c r="G142" t="n">
+        <v>5.479166666666667</v>
+      </c>
+      <c r="H142" t="n">
+        <v>32</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ZDF heute-show</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>4.431818181818182</v>
+      </c>
+      <c r="C143" t="n">
+        <v>4.3125</v>
+      </c>
+      <c r="D143" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E143" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F143" t="n">
+        <v>4.425</v>
+      </c>
+      <c r="G143" t="n">
+        <v>4.238095238095238</v>
+      </c>
+      <c r="H143" t="n">
+        <v>24</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ZDFheute Nachrichten</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D144" t="n">
+        <v>5</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>4.958333333333333</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1.708333333333333</v>
+      </c>
+      <c r="H144" t="n">
+        <v>25</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ZDFtivi</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>4.769230769230769</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>5</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>4.769230769230769</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>27</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>_horizont_</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>5.615384615384615</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3.115384615384615</v>
+      </c>
+      <c r="D146" t="n">
+        <v>5</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H146" t="n">
+        <v>13</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>acTVism Munich</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C147" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D147" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E147" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F147" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G147" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H147" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>achse:ostwest</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>8.208333333333334</v>
+      </c>
+      <c r="C148" t="n">
+        <v>7.916666666666667</v>
+      </c>
+      <c r="D148" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E148" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F148" t="n">
+        <v>8.214285714285714</v>
+      </c>
+      <c r="G148" t="n">
+        <v>8.142857142857142</v>
+      </c>
+      <c r="H148" t="n">
+        <v>12</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>congstar</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>3</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D149" t="n">
+        <v>3</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>3</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H149" t="n">
+        <v>6</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>eigentümlich frei</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>8.137837837837839</v>
+      </c>
+      <c r="C150" t="n">
+        <v>7.237837837837838</v>
+      </c>
+      <c r="D150" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E150" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F150" t="n">
+        <v>8.303333333333333</v>
+      </c>
+      <c r="G150" t="n">
+        <v>7.326666666666667</v>
+      </c>
+      <c r="H150" t="n">
+        <v>40</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>euronews (deutsch)</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>5</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D151" t="n">
+        <v>5</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>5</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H151" t="n">
+        <v>44</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0.4318181818181818</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0.4318181818181818</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>extra 3</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>4</v>
+      </c>
+      <c r="C152" t="n">
+        <v>3.963414634146341</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E152" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F152" t="n">
+        <v>4.073529411764706</v>
+      </c>
+      <c r="G152" t="n">
+        <v>3.986111111111111</v>
+      </c>
+      <c r="H152" t="n">
+        <v>60</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>exxpressTV</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C153" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D153" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E153" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F153" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G153" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H153" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>faz</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>4.793103448275862</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="D154" t="n">
+        <v>5</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>4.785714285714286</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H154" t="n">
+        <v>31</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>hessenschau</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>5</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>30</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>münchen.tv</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>4.608695652173913</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1.260869565217391</v>
+      </c>
+      <c r="D156" t="n">
+        <v>5</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>4.608695652173913</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1.260869565217391</v>
+      </c>
+      <c r="H156" t="n">
+        <v>60</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.6166666666666667</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0.6166666666666667</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>phoenix</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>4.574193548387097</v>
+      </c>
+      <c r="C157" t="n">
+        <v>2.032258064516129</v>
+      </c>
+      <c r="D157" t="n">
+        <v>5</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>4.596551724137932</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2.172413793103448</v>
+      </c>
+      <c r="H157" t="n">
+        <v>32</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0.03125</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>quer</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="D158" t="n">
+        <v>5</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H158" t="n">
+        <v>7</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ran Bundesliga</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C159" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D159" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E159" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F159" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G159" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H159" t="n">
+        <v>60</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.9833333333333333</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>rbb</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H160" t="n">
+        <v>18</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>stern</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>5</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>5</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>stern TV</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>4.522727272727272</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1.434782608695652</v>
+      </c>
+      <c r="D162" t="n">
+        <v>5</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4.522727272727272</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1.434782608695652</v>
+      </c>
+      <c r="H162" t="n">
+        <v>37</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.4054054054054054</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>taff</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D163" t="n">
+        <v>5</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="H163" t="n">
+        <v>60</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>tagesschau</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>4.744444444444444</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="D164" t="n">
+        <v>5</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="n">
+        <v>4.744444444444444</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="H164" t="n">
+        <v>39</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.05128205128205128</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
           <t>tvberlin</t>
         </is>
       </c>
-      <c r="B117" t="n">
+      <c r="B165" t="n">
         <v>6.020833333333333</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C165" t="n">
         <v>3.291666666666667</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D165" t="n">
         <v>5.5</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E165" t="n">
         <v>3.5</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F165" t="n">
         <v>6.020833333333333</v>
       </c>
-      <c r="G117" t="n">
+      <c r="G165" t="n">
         <v>3.291666666666667</v>
       </c>
-      <c r="H117" t="n">
+      <c r="H165" t="n">
         <v>27</v>
       </c>
-      <c r="I117" t="n">
+      <c r="I165" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="J117" t="n">
+      <c r="J165" t="n">
         <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>zeitzeugen-portal</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>4.613207547169812</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.4811320754716981</v>
+      </c>
+      <c r="D166" t="n">
+        <v>5</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" t="n">
+        <v>4.613207547169812</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.4811320754716981</v>
+      </c>
+      <c r="H166" t="n">
+        <v>60</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0.1166666666666667</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0.1166666666666667</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Österreich zuerst</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>7.117021276595745</v>
+      </c>
+      <c r="C167" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D167" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E167" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F167" t="n">
+        <v>7.147727272727272</v>
+      </c>
+      <c r="G167" t="n">
+        <v>6.534090909090909</v>
+      </c>
+      <c r="H167" t="n">
+        <v>47</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
